--- a/cuadros/ABRIL/ABRIL_GUACARA_IPSFA.xlsx
+++ b/cuadros/ABRIL/ABRIL_GUACARA_IPSFA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\ABRIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D344AF93-B799-4933-ADCB-CA49CE73F407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62664338-9C89-4933-85B8-FF581645798B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -347,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -362,6 +362,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,7 +745,7 @@
       <c r="I2" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="8">
         <v>140</v>
       </c>
     </row>
@@ -870,7 +871,7 @@
       <c r="I6" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="8">
         <v>473.92</v>
       </c>
     </row>
@@ -984,7 +985,7 @@
       <c r="I10" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="8">
         <v>82.12</v>
       </c>
     </row>

--- a/cuadros/ABRIL/ABRIL_GUACARA_IPSFA.xlsx
+++ b/cuadros/ABRIL/ABRIL_GUACARA_IPSFA.xlsx
@@ -1,302 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\FISCALIZACION\cuadros\ABRIL\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62664338-9C89-4933-85B8-FF581645798B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="REFERENCIA" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REFERENCIA" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="80">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-  </si>
-  <si>
-    <t>TIPO A</t>
-  </si>
-  <si>
-    <t>FALTA SELLO, FIRMA O CÉDULA.</t>
-  </si>
-  <si>
-    <t>DOCUMENTO NO LEGIBLE</t>
-  </si>
-  <si>
-    <t>DOCUMENTACIÓN ERRÓNEA</t>
-  </si>
-  <si>
-    <t>TIPO B</t>
-  </si>
-  <si>
-    <t>FISCALIZACIÓN A DESTIEMPO</t>
-  </si>
-  <si>
-    <t>PRODUCTO O SKU DUPLICADO.</t>
-  </si>
-  <si>
-    <t>RECEPCIÓN FUERA DE VISUAL / CON OBSTRUCCIÓN.</t>
-  </si>
-  <si>
-    <t>FISCALIZACIÓN CON USUARIO NO CORRESPONDIENTE</t>
-  </si>
-  <si>
-    <t>TIPO C</t>
-  </si>
-  <si>
-    <t>ERROR DE KG EN TARA.</t>
-  </si>
-  <si>
-    <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
-  </si>
-  <si>
-    <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
-  </si>
-  <si>
-    <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
-  </si>
-  <si>
-    <t>TIPO D</t>
-  </si>
-  <si>
-    <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
-  </si>
-  <si>
-    <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
-  </si>
-  <si>
-    <t>TIPO E</t>
-  </si>
-  <si>
-    <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
-  </si>
-  <si>
-    <t>GUACARA</t>
-  </si>
-  <si>
-    <t>IPSFA</t>
-  </si>
-  <si>
-    <t>LATIN FRUTS</t>
-  </si>
-  <si>
-    <t>ECO CARNES</t>
-  </si>
-  <si>
-    <t>MUSACEUM</t>
-  </si>
-  <si>
-    <t>VICAR</t>
-  </si>
-  <si>
-    <t>PARADIS FRESH</t>
-  </si>
-  <si>
-    <t>LA PATRONA 2024</t>
-  </si>
-  <si>
-    <t>RUBYMAR</t>
-  </si>
-  <si>
-    <t>FRUMIX</t>
-  </si>
-  <si>
-    <t>SANARE</t>
-  </si>
-  <si>
-    <t>JEAN DAVID</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>JOSE MAUREL</t>
-  </si>
-  <si>
-    <t>ROBERT NUÑEZ</t>
-  </si>
-  <si>
-    <t>NIXILETH ARRIZGA</t>
-  </si>
-  <si>
-    <t>ELYS BOLIVAR</t>
-  </si>
-  <si>
-    <t>DOUGLAS BUSTAMANTE</t>
-  </si>
-  <si>
-    <t>GABRIELA VIVAS</t>
-  </si>
-  <si>
-    <t>ELYANNYS VILLEGAS</t>
-  </si>
-  <si>
-    <t>JHON SINISTERRA</t>
-  </si>
-  <si>
-    <t>YUSBELIS MONTILLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGOSTINO NO LLEGA EN LA RECEPCION </t>
-  </si>
-  <si>
-    <t>FiSCALIZACION A DESTIEMPO</t>
-  </si>
-  <si>
-    <t>FALTANTE DE 200GR DE CAMBUR</t>
-  </si>
-  <si>
-    <t>FALTANTE DE 400 GR DE LECHUGA CRIOLLA</t>
-  </si>
-  <si>
-    <t>RECEPCION CON OBSTRUCCION</t>
-  </si>
-  <si>
-    <t>FISCALIZACION A DESTIEMPO</t>
-  </si>
-  <si>
-    <t>SE BORRA LA FISCALIZACION POR NO COMPLETAR EL PROCESO</t>
-  </si>
-  <si>
-    <t>SE CARGO EL DOCUMENTO EQUIVOCADO</t>
-  </si>
-  <si>
-    <t>NO SE FISCALIZO 13,8 KG DE NARANJA IMPORTADA</t>
-  </si>
-  <si>
-    <t>FALTANTE DE 200GR DE PARCHITA</t>
-  </si>
-  <si>
-    <t>ERROR EN TARA DE CHAYOTA 3KG DE DIFERENCIA</t>
-  </si>
-  <si>
-    <t>SKU DUPLICADO</t>
-  </si>
-  <si>
-    <t>DIFERENCIA DE PESAJE EN TARA LECHUGA 4,2KG, NO SE FISCALIZO EL ROMERO 2,1KG</t>
-  </si>
-  <si>
-    <t>DIFERENCIA DE TARA EN LOS TRASTES 6KG</t>
-  </si>
-  <si>
-    <t>NO SE FISCALIZARON LOS TRASTES</t>
-  </si>
-  <si>
-    <t>00003748</t>
-  </si>
-  <si>
-    <t>ELIANNYS VILLEGAS</t>
-  </si>
-  <si>
-    <t>00114739</t>
-  </si>
-  <si>
-    <t>00170489</t>
-  </si>
-  <si>
-    <t>LOS SAMANES</t>
-  </si>
-  <si>
-    <t>MARCIA QUEVEDO</t>
-  </si>
-  <si>
-    <t>SE CARGARON LAS TARAS EN 2,3KG Y SON DE 2,2KG GENERA UN FALTANTE DE 500GR</t>
-  </si>
-  <si>
-    <t>CAVA LUXOR</t>
-  </si>
-  <si>
-    <t>SKU EQUIVOCADO NO PERTENECE A LA RECEPCION</t>
-  </si>
-  <si>
-    <t>CORVARA</t>
-  </si>
-  <si>
-    <t>RICARDO RUIZ</t>
-  </si>
-  <si>
-    <t>SE CARGO EL SKU UNA HORA DESPUES DE HACER EL PESAJE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -348,35 +86,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -664,3736 +461,4076 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L500"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="17.84375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="55" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="72.15234375" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="12" style="7" customWidth="1"/>
+    <col width="15" customWidth="1" style="8" min="1" max="1"/>
+    <col width="20" customWidth="1" style="8" min="2" max="2"/>
+    <col width="15" customWidth="1" style="8" min="3" max="3"/>
+    <col width="17.84375" customWidth="1" style="3" min="4" max="4"/>
+    <col width="20" customWidth="1" style="8" min="5" max="5"/>
+    <col width="22" customWidth="1" style="8" min="6" max="6"/>
+    <col width="55" customWidth="1" style="8" min="7" max="7"/>
+    <col width="15" customWidth="1" style="8" min="8" max="8"/>
+    <col width="72.15234375" customWidth="1" style="8" min="9" max="9"/>
+    <col width="12" customWidth="1" style="8" min="10" max="10"/>
+    <col width="12" customWidth="1" style="7" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ECO CARNES</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12705</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>JHON SINISTERRA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H2">
+        <f>IF(G2="","",VLOOKUP(G2,REFERENCIA!$A$1:$B$15,2,0))</f>
+        <v/>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NO SE FISCALIZARON LOS TRASTES</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ECO CARNES</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12659</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>YUSBELIS MONTILLA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H3">
+        <f>IF(G3="","",VLOOKUP(G3,REFERENCIA!$A$1:$B$15,2,0))</f>
+        <v/>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DIFERENCIA DE TARA EN LOS TRASTES 6KG</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2">
-        <v>12705</v>
-      </c>
-      <c r="D2" s="3">
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>VICAR</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13338</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>46113</v>
       </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="str">
-        <f>IF(G2="","",VLOOKUP(G2,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I2" t="s">
-        <v>67</v>
-      </c>
-      <c r="J2" s="8">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3">
-        <v>12659</v>
-      </c>
-      <c r="D3" s="3">
-        <v>46113</v>
-      </c>
-      <c r="E3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="str">
-        <f>IF(G3="","",VLOOKUP(G3,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4">
-        <v>13338</v>
-      </c>
-      <c r="D4" s="3">
-        <v>46113</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="str">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>JHON SINISTERRA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H4">
         <f>IF(G4="","",VLOOKUP(G4,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5">
+        <v/>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DIFERENCIA DE PESAJE EN TARA LECHUGA 4,2KG, NO SE FISCALIZO EL ROMERO 2,1KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JEAN DAVID</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>19069</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="3" t="n">
         <v>46119</v>
       </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="str">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ELYS BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H5">
         <f>IF(G5="","",VLOOKUP(G5,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6">
+        <v/>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SKU DUPLICADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LA PATRONA 2024</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>408</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="3" t="n">
         <v>46115</v>
       </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" t="str">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JHON SINISTERRA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H6">
         <f>IF(G6="","",VLOOKUP(G6,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO E</v>
-      </c>
-      <c r="I6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="8">
+        <v/>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SE BORRA LA FISCALIZACION POR NO COMPLETAR EL PROCESO</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>473.92</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VICAR</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>13369</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="3" t="n">
         <v>46120</v>
       </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" t="str">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>JOSE MAUREL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H7">
         <f>IF(G7="","",VLOOKUP(G7,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="5">
+        <v/>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ERROR EN TARA DE CHAYOTA 3KG DE DIFERENCIA</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" t="str">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SANARE</t>
+        </is>
+      </c>
+      <c r="H8">
         <f>IF(G8="","",VLOOKUP(G8,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LA PATRONA 2024</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>430</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="n">
         <v>46121</v>
       </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" t="str">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>JOSE MAUREL</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H9">
         <f>IF(G9="","",VLOOKUP(G9,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO D</v>
-      </c>
-      <c r="I9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" s="4">
+        <v/>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FALTANTE DE 200GR DE PARCHITA</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10">
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>00170489</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FRUMIX</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>9356</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="n">
         <v>46122</v>
       </c>
-      <c r="E10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" t="str">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ELYANNYS VILLEGAS</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H10">
         <f>IF(G10="","",VLOOKUP(G10,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I10" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" s="8">
+        <v/>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>NO SE FISCALIZO 13,8 KG DE NARANJA IMPORTADA</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>82.12</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PARADIS FRESH</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>23430</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="3" t="n">
         <v>46122</v>
       </c>
-      <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" t="str">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>GABRIELA VIVAS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H11">
         <f>IF(G11="","",VLOOKUP(G11,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12">
+        <v/>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SE CARGO EL DOCUMENTO EQUIVOCADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LA PATRONA 2024</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>6134</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="n">
         <v>46122</v>
       </c>
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" t="str">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>GABRIELA VIVAS</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="H12">
         <f>IF(G12="","",VLOOKUP(G12,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO E</v>
-      </c>
-      <c r="I12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13">
+        <v/>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SE BORRA LA FISCALIZACION POR NO COMPLETAR EL PROCESO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RUBYMAR</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>8683</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="3" t="n">
         <v>46128</v>
       </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" t="str">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DOUGLAS BUSTAMANTE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H13">
         <f>IF(G13="","",VLOOKUP(G13,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="3">
+        <v/>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FISCALIZACION A DESTIEMPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA PATRONA 2024</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>46128</v>
       </c>
-      <c r="E14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" t="str">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DOUGLAS BUSTAMANTE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H14">
         <f>IF(G14="","",VLOOKUP(G14,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15">
+        <v/>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FISCALIZACION A DESTIEMPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PARADIS FRESH</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>23847</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="3" t="n">
         <v>46129</v>
       </c>
-      <c r="E15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" t="str">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ELYS BOLIVAR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN FUERA DE VISUAL / CON OBSTRUCCIÓN.</t>
+        </is>
+      </c>
+      <c r="H15">
         <f>IF(G15="","",VLOOKUP(G15,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16">
+        <v/>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RECEPCION CON OBSTRUCCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VICAR</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>13439</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="3" t="n">
         <v>46129</v>
       </c>
-      <c r="E16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" t="str">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JOSE MAUREL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H16">
         <f>IF(G16="","",VLOOKUP(G16,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO D</v>
-      </c>
-      <c r="I16" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="4">
+        <v/>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FALTANTE DE 400 GR DE LECHUGA CRIOLLA</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17">
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>00114739</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MUSACEUM</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>12912</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="n">
         <v>46129</v>
       </c>
-      <c r="E17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" t="str">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NIXILETH ARRIZGA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H17">
         <f>IF(G17="","",VLOOKUP(G17,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO D</v>
-      </c>
-      <c r="I17" t="s">
-        <v>55</v>
-      </c>
-      <c r="J17" s="4">
+        <v/>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>FALTANTE DE 200GR DE CAMBUR</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18">
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>00003748</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ECO CARNES</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>3947</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="n">
         <v>46133</v>
       </c>
-      <c r="E18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" t="str">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ROBERT NUÑEZ</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H18">
         <f>IF(G18="","",VLOOKUP(G18,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19">
+        <v/>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FiSCALIZACION A DESTIEMPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LATIN FRUTS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>6384</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="3" t="n">
         <v>46139</v>
       </c>
-      <c r="E19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" t="str">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>JOSE MAUREL</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H19">
         <f>IF(G19="","",VLOOKUP(G19,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20">
+        <v/>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANGOSTINO NO LLEGA EN LA RECEPCION </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LATIN FRUTS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>6427</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="n">
         <v>46140</v>
       </c>
-      <c r="E20" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" t="str">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ELIANNYS VILLEGAS</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H20">
         <f>IF(G20="","",VLOOKUP(G20,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21">
+        <v/>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SE CARGO EL DOCUMENTO EQUIVOCADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LOS SAMANES</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>5137</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="n">
         <v>46140</v>
       </c>
-      <c r="E21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" t="str">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MARCIA QUEVEDO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H21">
         <f>IF(G21="","",VLOOKUP(G21,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I21" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" s="5">
+        <v/>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SE CARGARON LAS TARAS EN 2,3KG Y SON DE 2,2KG GENERA UN FALTANTE DE 500GR</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="n">
         <v>0.17</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22">
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>106749</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="n">
         <v>45777</v>
       </c>
-      <c r="E22" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" t="str">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GABRIELA VIVAS</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H22">
         <f>IF(G22="","",VLOOKUP(G22,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO C</v>
-      </c>
-      <c r="I22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23">
+        <v/>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SKU EQUIVOCADO NO PERTENECE A LA RECEPCION</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IPSFA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CORVARA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>31047</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="n">
         <v>45777</v>
       </c>
-      <c r="E23" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" t="str">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>RICARDO RUIZ</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H23">
         <f>IF(G23="","",VLOOKUP(G23,REFERENCIA!$A$1:$B$15,2,0))</f>
-        <v>TIPO B</v>
-      </c>
-      <c r="I23" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SE CARGO EL SKU UNA HORA DESPUES DE HACER EL PESAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24">
         <f>IF(G24="","",VLOOKUP(G24,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H25" t="str">
+    <row r="25">
+      <c r="H25">
         <f>IF(G25="","",VLOOKUP(G25,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H26" t="str">
+    <row r="26">
+      <c r="H26">
         <f>IF(G26="","",VLOOKUP(G26,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H27" t="str">
+    <row r="27">
+      <c r="H27">
         <f>IF(G27="","",VLOOKUP(G27,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H28" t="str">
+    <row r="28">
+      <c r="H28">
         <f>IF(G28="","",VLOOKUP(G28,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H29" t="str">
+    <row r="29">
+      <c r="H29">
         <f>IF(G29="","",VLOOKUP(G29,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H30" t="str">
+    <row r="30">
+      <c r="H30">
         <f>IF(G30="","",VLOOKUP(G30,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H31" t="str">
+    <row r="31">
+      <c r="H31">
         <f>IF(G31="","",VLOOKUP(G31,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="H32" t="str">
+    <row r="32">
+      <c r="H32">
         <f>IF(G32="","",VLOOKUP(G32,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H33" t="str">
+    <row r="33">
+      <c r="H33">
         <f>IF(G33="","",VLOOKUP(G33,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H34" t="str">
+    <row r="34">
+      <c r="H34">
         <f>IF(G34="","",VLOOKUP(G34,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H35" t="str">
+    <row r="35">
+      <c r="H35">
         <f>IF(G35="","",VLOOKUP(G35,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H36" t="str">
+    <row r="36">
+      <c r="H36">
         <f>IF(G36="","",VLOOKUP(G36,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H37" t="str">
+    <row r="37">
+      <c r="H37">
         <f>IF(G37="","",VLOOKUP(G37,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H38" t="str">
+    <row r="38">
+      <c r="H38">
         <f>IF(G38="","",VLOOKUP(G38,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H39" t="str">
+    <row r="39">
+      <c r="H39">
         <f>IF(G39="","",VLOOKUP(G39,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H40" t="str">
+    <row r="40">
+      <c r="H40">
         <f>IF(G40="","",VLOOKUP(G40,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H41" t="str">
+    <row r="41">
+      <c r="H41">
         <f>IF(G41="","",VLOOKUP(G41,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H42" t="str">
+    <row r="42">
+      <c r="H42">
         <f>IF(G42="","",VLOOKUP(G42,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H43" t="str">
+    <row r="43">
+      <c r="H43">
         <f>IF(G43="","",VLOOKUP(G43,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H44" t="str">
+    <row r="44">
+      <c r="H44">
         <f>IF(G44="","",VLOOKUP(G44,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H45" t="str">
+    <row r="45">
+      <c r="H45">
         <f>IF(G45="","",VLOOKUP(G45,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H46" t="str">
+    <row r="46">
+      <c r="H46">
         <f>IF(G46="","",VLOOKUP(G46,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H47" t="str">
+    <row r="47">
+      <c r="H47">
         <f>IF(G47="","",VLOOKUP(G47,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H48" t="str">
+    <row r="48">
+      <c r="H48">
         <f>IF(G48="","",VLOOKUP(G48,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H49" t="str">
+    <row r="49">
+      <c r="H49">
         <f>IF(G49="","",VLOOKUP(G49,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H50" t="str">
+    <row r="50">
+      <c r="H50">
         <f>IF(G50="","",VLOOKUP(G50,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H51" t="str">
+    <row r="51">
+      <c r="H51">
         <f>IF(G51="","",VLOOKUP(G51,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H52" t="str">
+    <row r="52">
+      <c r="H52">
         <f>IF(G52="","",VLOOKUP(G52,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H53" t="str">
+    <row r="53">
+      <c r="H53">
         <f>IF(G53="","",VLOOKUP(G53,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H54" t="str">
+    <row r="54">
+      <c r="H54">
         <f>IF(G54="","",VLOOKUP(G54,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H55" t="str">
+    <row r="55">
+      <c r="H55">
         <f>IF(G55="","",VLOOKUP(G55,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H56" t="str">
+    <row r="56">
+      <c r="H56">
         <f>IF(G56="","",VLOOKUP(G56,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H57" t="str">
+    <row r="57">
+      <c r="H57">
         <f>IF(G57="","",VLOOKUP(G57,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H58" t="str">
+    <row r="58">
+      <c r="H58">
         <f>IF(G58="","",VLOOKUP(G58,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H59" t="str">
+    <row r="59">
+      <c r="H59">
         <f>IF(G59="","",VLOOKUP(G59,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H60" t="str">
+    <row r="60">
+      <c r="H60">
         <f>IF(G60="","",VLOOKUP(G60,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H61" t="str">
+    <row r="61">
+      <c r="H61">
         <f>IF(G61="","",VLOOKUP(G61,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H62" t="str">
+    <row r="62">
+      <c r="H62">
         <f>IF(G62="","",VLOOKUP(G62,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H63" t="str">
+    <row r="63">
+      <c r="H63">
         <f>IF(G63="","",VLOOKUP(G63,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H64" t="str">
+    <row r="64">
+      <c r="H64">
         <f>IF(G64="","",VLOOKUP(G64,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H65" t="str">
+    <row r="65">
+      <c r="H65">
         <f>IF(G65="","",VLOOKUP(G65,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H66" t="str">
+    <row r="66">
+      <c r="H66">
         <f>IF(G66="","",VLOOKUP(G66,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H67" t="str">
+    <row r="67">
+      <c r="H67">
         <f>IF(G67="","",VLOOKUP(G67,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H68" t="str">
+    <row r="68">
+      <c r="H68">
         <f>IF(G68="","",VLOOKUP(G68,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H69" t="str">
+    <row r="69">
+      <c r="H69">
         <f>IF(G69="","",VLOOKUP(G69,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H70" t="str">
+    <row r="70">
+      <c r="H70">
         <f>IF(G70="","",VLOOKUP(G70,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H71" t="str">
+    <row r="71">
+      <c r="H71">
         <f>IF(G71="","",VLOOKUP(G71,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H72" t="str">
+    <row r="72">
+      <c r="H72">
         <f>IF(G72="","",VLOOKUP(G72,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H73" t="str">
+    <row r="73">
+      <c r="H73">
         <f>IF(G73="","",VLOOKUP(G73,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H74" t="str">
+    <row r="74">
+      <c r="H74">
         <f>IF(G74="","",VLOOKUP(G74,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H75" t="str">
+    <row r="75">
+      <c r="H75">
         <f>IF(G75="","",VLOOKUP(G75,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H76" t="str">
+    <row r="76">
+      <c r="H76">
         <f>IF(G76="","",VLOOKUP(G76,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H77" t="str">
+    <row r="77">
+      <c r="H77">
         <f>IF(G77="","",VLOOKUP(G77,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H78" t="str">
+    <row r="78">
+      <c r="H78">
         <f>IF(G78="","",VLOOKUP(G78,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H79" t="str">
+    <row r="79">
+      <c r="H79">
         <f>IF(G79="","",VLOOKUP(G79,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H80" t="str">
+    <row r="80">
+      <c r="H80">
         <f>IF(G80="","",VLOOKUP(G80,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H81" t="str">
+    <row r="81">
+      <c r="H81">
         <f>IF(G81="","",VLOOKUP(G81,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H82" t="str">
+    <row r="82">
+      <c r="H82">
         <f>IF(G82="","",VLOOKUP(G82,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H83" t="str">
+    <row r="83">
+      <c r="H83">
         <f>IF(G83="","",VLOOKUP(G83,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H84" t="str">
+    <row r="84">
+      <c r="H84">
         <f>IF(G84="","",VLOOKUP(G84,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H85" t="str">
+    <row r="85">
+      <c r="H85">
         <f>IF(G85="","",VLOOKUP(G85,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H86" t="str">
+    <row r="86">
+      <c r="H86">
         <f>IF(G86="","",VLOOKUP(G86,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H87" t="str">
+    <row r="87">
+      <c r="H87">
         <f>IF(G87="","",VLOOKUP(G87,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H88" t="str">
+    <row r="88">
+      <c r="H88">
         <f>IF(G88="","",VLOOKUP(G88,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H89" t="str">
+    <row r="89">
+      <c r="H89">
         <f>IF(G89="","",VLOOKUP(G89,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H90" t="str">
+    <row r="90">
+      <c r="H90">
         <f>IF(G90="","",VLOOKUP(G90,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H91" t="str">
+    <row r="91">
+      <c r="H91">
         <f>IF(G91="","",VLOOKUP(G91,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H92" t="str">
+    <row r="92">
+      <c r="H92">
         <f>IF(G92="","",VLOOKUP(G92,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H93" t="str">
+    <row r="93">
+      <c r="H93">
         <f>IF(G93="","",VLOOKUP(G93,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H94" t="str">
+    <row r="94">
+      <c r="H94">
         <f>IF(G94="","",VLOOKUP(G94,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H95" t="str">
+    <row r="95">
+      <c r="H95">
         <f>IF(G95="","",VLOOKUP(G95,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H96" t="str">
+    <row r="96">
+      <c r="H96">
         <f>IF(G96="","",VLOOKUP(G96,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H97" t="str">
+    <row r="97">
+      <c r="H97">
         <f>IF(G97="","",VLOOKUP(G97,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H98" t="str">
+    <row r="98">
+      <c r="H98">
         <f>IF(G98="","",VLOOKUP(G98,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H99" t="str">
+    <row r="99">
+      <c r="H99">
         <f>IF(G99="","",VLOOKUP(G99,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H100" t="str">
+    <row r="100">
+      <c r="H100">
         <f>IF(G100="","",VLOOKUP(G100,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H101" t="str">
+    <row r="101">
+      <c r="H101">
         <f>IF(G101="","",VLOOKUP(G101,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H102" t="str">
+    <row r="102">
+      <c r="H102">
         <f>IF(G102="","",VLOOKUP(G102,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H103" t="str">
+    <row r="103">
+      <c r="H103">
         <f>IF(G103="","",VLOOKUP(G103,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H104" t="str">
+    <row r="104">
+      <c r="H104">
         <f>IF(G104="","",VLOOKUP(G104,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H105" t="str">
+    <row r="105">
+      <c r="H105">
         <f>IF(G105="","",VLOOKUP(G105,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H106" t="str">
+    <row r="106">
+      <c r="H106">
         <f>IF(G106="","",VLOOKUP(G106,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H107" t="str">
+    <row r="107">
+      <c r="H107">
         <f>IF(G107="","",VLOOKUP(G107,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H108" t="str">
+    <row r="108">
+      <c r="H108">
         <f>IF(G108="","",VLOOKUP(G108,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H109" t="str">
+    <row r="109">
+      <c r="H109">
         <f>IF(G109="","",VLOOKUP(G109,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H110" t="str">
+    <row r="110">
+      <c r="H110">
         <f>IF(G110="","",VLOOKUP(G110,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H111" t="str">
+    <row r="111">
+      <c r="H111">
         <f>IF(G111="","",VLOOKUP(G111,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H112" t="str">
+    <row r="112">
+      <c r="H112">
         <f>IF(G112="","",VLOOKUP(G112,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H113" t="str">
+    <row r="113">
+      <c r="H113">
         <f>IF(G113="","",VLOOKUP(G113,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H114" t="str">
+    <row r="114">
+      <c r="H114">
         <f>IF(G114="","",VLOOKUP(G114,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H115" t="str">
+    <row r="115">
+      <c r="H115">
         <f>IF(G115="","",VLOOKUP(G115,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H116" t="str">
+    <row r="116">
+      <c r="H116">
         <f>IF(G116="","",VLOOKUP(G116,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H117" t="str">
+    <row r="117">
+      <c r="H117">
         <f>IF(G117="","",VLOOKUP(G117,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H118" t="str">
+    <row r="118">
+      <c r="H118">
         <f>IF(G118="","",VLOOKUP(G118,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H119" t="str">
+    <row r="119">
+      <c r="H119">
         <f>IF(G119="","",VLOOKUP(G119,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H120" t="str">
+    <row r="120">
+      <c r="H120">
         <f>IF(G120="","",VLOOKUP(G120,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H121" t="str">
+    <row r="121">
+      <c r="H121">
         <f>IF(G121="","",VLOOKUP(G121,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H122" t="str">
+    <row r="122">
+      <c r="H122">
         <f>IF(G122="","",VLOOKUP(G122,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H123" t="str">
+    <row r="123">
+      <c r="H123">
         <f>IF(G123="","",VLOOKUP(G123,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H124" t="str">
+    <row r="124">
+      <c r="H124">
         <f>IF(G124="","",VLOOKUP(G124,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H125" t="str">
+    <row r="125">
+      <c r="H125">
         <f>IF(G125="","",VLOOKUP(G125,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H126" t="str">
+    <row r="126">
+      <c r="H126">
         <f>IF(G126="","",VLOOKUP(G126,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H127" t="str">
+    <row r="127">
+      <c r="H127">
         <f>IF(G127="","",VLOOKUP(G127,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H128" t="str">
+    <row r="128">
+      <c r="H128">
         <f>IF(G128="","",VLOOKUP(G128,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H129" t="str">
+    <row r="129">
+      <c r="H129">
         <f>IF(G129="","",VLOOKUP(G129,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H130" t="str">
+    <row r="130">
+      <c r="H130">
         <f>IF(G130="","",VLOOKUP(G130,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="131" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H131" t="str">
+    <row r="131">
+      <c r="H131">
         <f>IF(G131="","",VLOOKUP(G131,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="132" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H132" t="str">
+    <row r="132">
+      <c r="H132">
         <f>IF(G132="","",VLOOKUP(G132,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="133" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H133" t="str">
+    <row r="133">
+      <c r="H133">
         <f>IF(G133="","",VLOOKUP(G133,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="134" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H134" t="str">
+    <row r="134">
+      <c r="H134">
         <f>IF(G134="","",VLOOKUP(G134,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="135" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H135" t="str">
+    <row r="135">
+      <c r="H135">
         <f>IF(G135="","",VLOOKUP(G135,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H136" t="str">
+    <row r="136">
+      <c r="H136">
         <f>IF(G136="","",VLOOKUP(G136,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="137" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H137" t="str">
+    <row r="137">
+      <c r="H137">
         <f>IF(G137="","",VLOOKUP(G137,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="138" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H138" t="str">
+    <row r="138">
+      <c r="H138">
         <f>IF(G138="","",VLOOKUP(G138,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="139" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H139" t="str">
+    <row r="139">
+      <c r="H139">
         <f>IF(G139="","",VLOOKUP(G139,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H140" t="str">
+    <row r="140">
+      <c r="H140">
         <f>IF(G140="","",VLOOKUP(G140,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H141" t="str">
+    <row r="141">
+      <c r="H141">
         <f>IF(G141="","",VLOOKUP(G141,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="142" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H142" t="str">
+    <row r="142">
+      <c r="H142">
         <f>IF(G142="","",VLOOKUP(G142,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="143" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H143" t="str">
+    <row r="143">
+      <c r="H143">
         <f>IF(G143="","",VLOOKUP(G143,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="144" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H144" t="str">
+    <row r="144">
+      <c r="H144">
         <f>IF(G144="","",VLOOKUP(G144,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H145" t="str">
+    <row r="145">
+      <c r="H145">
         <f>IF(G145="","",VLOOKUP(G145,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="146" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H146" t="str">
+    <row r="146">
+      <c r="H146">
         <f>IF(G146="","",VLOOKUP(G146,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="147" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H147" t="str">
+    <row r="147">
+      <c r="H147">
         <f>IF(G147="","",VLOOKUP(G147,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H148" t="str">
+    <row r="148">
+      <c r="H148">
         <f>IF(G148="","",VLOOKUP(G148,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H149" t="str">
+    <row r="149">
+      <c r="H149">
         <f>IF(G149="","",VLOOKUP(G149,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="150" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H150" t="str">
+    <row r="150">
+      <c r="H150">
         <f>IF(G150="","",VLOOKUP(G150,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="151" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H151" t="str">
+    <row r="151">
+      <c r="H151">
         <f>IF(G151="","",VLOOKUP(G151,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="152" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H152" t="str">
+    <row r="152">
+      <c r="H152">
         <f>IF(G152="","",VLOOKUP(G152,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H153" t="str">
+    <row r="153">
+      <c r="H153">
         <f>IF(G153="","",VLOOKUP(G153,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="154" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H154" t="str">
+    <row r="154">
+      <c r="H154">
         <f>IF(G154="","",VLOOKUP(G154,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="155" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H155" t="str">
+    <row r="155">
+      <c r="H155">
         <f>IF(G155="","",VLOOKUP(G155,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H156" t="str">
+    <row r="156">
+      <c r="H156">
         <f>IF(G156="","",VLOOKUP(G156,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H157" t="str">
+    <row r="157">
+      <c r="H157">
         <f>IF(G157="","",VLOOKUP(G157,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="158" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H158" t="str">
+    <row r="158">
+      <c r="H158">
         <f>IF(G158="","",VLOOKUP(G158,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="159" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H159" t="str">
+    <row r="159">
+      <c r="H159">
         <f>IF(G159="","",VLOOKUP(G159,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="160" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H160" t="str">
+    <row r="160">
+      <c r="H160">
         <f>IF(G160="","",VLOOKUP(G160,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H161" t="str">
+    <row r="161">
+      <c r="H161">
         <f>IF(G161="","",VLOOKUP(G161,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="162" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H162" t="str">
+    <row r="162">
+      <c r="H162">
         <f>IF(G162="","",VLOOKUP(G162,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="163" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H163" t="str">
+    <row r="163">
+      <c r="H163">
         <f>IF(G163="","",VLOOKUP(G163,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H164" t="str">
+    <row r="164">
+      <c r="H164">
         <f>IF(G164="","",VLOOKUP(G164,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H165" t="str">
+    <row r="165">
+      <c r="H165">
         <f>IF(G165="","",VLOOKUP(G165,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="166" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H166" t="str">
+    <row r="166">
+      <c r="H166">
         <f>IF(G166="","",VLOOKUP(G166,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="167" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H167" t="str">
+    <row r="167">
+      <c r="H167">
         <f>IF(G167="","",VLOOKUP(G167,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="168" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H168" t="str">
+    <row r="168">
+      <c r="H168">
         <f>IF(G168="","",VLOOKUP(G168,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H169" t="str">
+    <row r="169">
+      <c r="H169">
         <f>IF(G169="","",VLOOKUP(G169,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="170" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H170" t="str">
+    <row r="170">
+      <c r="H170">
         <f>IF(G170="","",VLOOKUP(G170,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="171" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H171" t="str">
+    <row r="171">
+      <c r="H171">
         <f>IF(G171="","",VLOOKUP(G171,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="172" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H172" t="str">
+    <row r="172">
+      <c r="H172">
         <f>IF(G172="","",VLOOKUP(G172,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="173" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H173" t="str">
+    <row r="173">
+      <c r="H173">
         <f>IF(G173="","",VLOOKUP(G173,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="174" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H174" t="str">
+    <row r="174">
+      <c r="H174">
         <f>IF(G174="","",VLOOKUP(G174,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="175" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H175" t="str">
+    <row r="175">
+      <c r="H175">
         <f>IF(G175="","",VLOOKUP(G175,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="176" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H176" t="str">
+    <row r="176">
+      <c r="H176">
         <f>IF(G176="","",VLOOKUP(G176,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H177" t="str">
+    <row r="177">
+      <c r="H177">
         <f>IF(G177="","",VLOOKUP(G177,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H178" t="str">
+    <row r="178">
+      <c r="H178">
         <f>IF(G178="","",VLOOKUP(G178,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H179" t="str">
+    <row r="179">
+      <c r="H179">
         <f>IF(G179="","",VLOOKUP(G179,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H180" t="str">
+    <row r="180">
+      <c r="H180">
         <f>IF(G180="","",VLOOKUP(G180,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H181" t="str">
+    <row r="181">
+      <c r="H181">
         <f>IF(G181="","",VLOOKUP(G181,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H182" t="str">
+    <row r="182">
+      <c r="H182">
         <f>IF(G182="","",VLOOKUP(G182,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H183" t="str">
+    <row r="183">
+      <c r="H183">
         <f>IF(G183="","",VLOOKUP(G183,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H184" t="str">
+    <row r="184">
+      <c r="H184">
         <f>IF(G184="","",VLOOKUP(G184,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H185" t="str">
+    <row r="185">
+      <c r="H185">
         <f>IF(G185="","",VLOOKUP(G185,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H186" t="str">
+    <row r="186">
+      <c r="H186">
         <f>IF(G186="","",VLOOKUP(G186,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H187" t="str">
+    <row r="187">
+      <c r="H187">
         <f>IF(G187="","",VLOOKUP(G187,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H188" t="str">
+    <row r="188">
+      <c r="H188">
         <f>IF(G188="","",VLOOKUP(G188,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H189" t="str">
+    <row r="189">
+      <c r="H189">
         <f>IF(G189="","",VLOOKUP(G189,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H190" t="str">
+    <row r="190">
+      <c r="H190">
         <f>IF(G190="","",VLOOKUP(G190,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H191" t="str">
+    <row r="191">
+      <c r="H191">
         <f>IF(G191="","",VLOOKUP(G191,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H192" t="str">
+    <row r="192">
+      <c r="H192">
         <f>IF(G192="","",VLOOKUP(G192,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="193" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H193" t="str">
+    <row r="193">
+      <c r="H193">
         <f>IF(G193="","",VLOOKUP(G193,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="194" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H194" t="str">
+    <row r="194">
+      <c r="H194">
         <f>IF(G194="","",VLOOKUP(G194,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="195" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H195" t="str">
+    <row r="195">
+      <c r="H195">
         <f>IF(G195="","",VLOOKUP(G195,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="196" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H196" t="str">
+    <row r="196">
+      <c r="H196">
         <f>IF(G196="","",VLOOKUP(G196,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="197" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H197" t="str">
+    <row r="197">
+      <c r="H197">
         <f>IF(G197="","",VLOOKUP(G197,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="198" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H198" t="str">
+    <row r="198">
+      <c r="H198">
         <f>IF(G198="","",VLOOKUP(G198,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="199" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H199" t="str">
+    <row r="199">
+      <c r="H199">
         <f>IF(G199="","",VLOOKUP(G199,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="200" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H200" t="str">
+    <row r="200">
+      <c r="H200">
         <f>IF(G200="","",VLOOKUP(G200,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="201" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H201" t="str">
+    <row r="201">
+      <c r="H201">
         <f>IF(G201="","",VLOOKUP(G201,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="202" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H202" t="str">
+    <row r="202">
+      <c r="H202">
         <f>IF(G202="","",VLOOKUP(G202,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="203" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H203" t="str">
+    <row r="203">
+      <c r="H203">
         <f>IF(G203="","",VLOOKUP(G203,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="204" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H204" t="str">
+    <row r="204">
+      <c r="H204">
         <f>IF(G204="","",VLOOKUP(G204,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="205" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H205" t="str">
+    <row r="205">
+      <c r="H205">
         <f>IF(G205="","",VLOOKUP(G205,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="206" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H206" t="str">
+    <row r="206">
+      <c r="H206">
         <f>IF(G206="","",VLOOKUP(G206,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="207" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H207" t="str">
+    <row r="207">
+      <c r="H207">
         <f>IF(G207="","",VLOOKUP(G207,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="208" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H208" t="str">
+    <row r="208">
+      <c r="H208">
         <f>IF(G208="","",VLOOKUP(G208,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H209" t="str">
+    <row r="209">
+      <c r="H209">
         <f>IF(G209="","",VLOOKUP(G209,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H210" t="str">
+    <row r="210">
+      <c r="H210">
         <f>IF(G210="","",VLOOKUP(G210,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H211" t="str">
+    <row r="211">
+      <c r="H211">
         <f>IF(G211="","",VLOOKUP(G211,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H212" t="str">
+    <row r="212">
+      <c r="H212">
         <f>IF(G212="","",VLOOKUP(G212,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H213" t="str">
+    <row r="213">
+      <c r="H213">
         <f>IF(G213="","",VLOOKUP(G213,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="214" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H214" t="str">
+    <row r="214">
+      <c r="H214">
         <f>IF(G214="","",VLOOKUP(G214,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="215" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H215" t="str">
+    <row r="215">
+      <c r="H215">
         <f>IF(G215="","",VLOOKUP(G215,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="216" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H216" t="str">
+    <row r="216">
+      <c r="H216">
         <f>IF(G216="","",VLOOKUP(G216,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="217" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H217" t="str">
+    <row r="217">
+      <c r="H217">
         <f>IF(G217="","",VLOOKUP(G217,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="218" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H218" t="str">
+    <row r="218">
+      <c r="H218">
         <f>IF(G218="","",VLOOKUP(G218,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="219" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H219" t="str">
+    <row r="219">
+      <c r="H219">
         <f>IF(G219="","",VLOOKUP(G219,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="220" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H220" t="str">
+    <row r="220">
+      <c r="H220">
         <f>IF(G220="","",VLOOKUP(G220,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="221" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H221" t="str">
+    <row r="221">
+      <c r="H221">
         <f>IF(G221="","",VLOOKUP(G221,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="222" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H222" t="str">
+    <row r="222">
+      <c r="H222">
         <f>IF(G222="","",VLOOKUP(G222,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="223" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H223" t="str">
+    <row r="223">
+      <c r="H223">
         <f>IF(G223="","",VLOOKUP(G223,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="224" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H224" t="str">
+    <row r="224">
+      <c r="H224">
         <f>IF(G224="","",VLOOKUP(G224,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="225" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H225" t="str">
+    <row r="225">
+      <c r="H225">
         <f>IF(G225="","",VLOOKUP(G225,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="226" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H226" t="str">
+    <row r="226">
+      <c r="H226">
         <f>IF(G226="","",VLOOKUP(G226,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="227" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H227" t="str">
+    <row r="227">
+      <c r="H227">
         <f>IF(G227="","",VLOOKUP(G227,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="228" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H228" t="str">
+    <row r="228">
+      <c r="H228">
         <f>IF(G228="","",VLOOKUP(G228,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="229" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H229" t="str">
+    <row r="229">
+      <c r="H229">
         <f>IF(G229="","",VLOOKUP(G229,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="230" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H230" t="str">
+    <row r="230">
+      <c r="H230">
         <f>IF(G230="","",VLOOKUP(G230,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="231" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H231" t="str">
+    <row r="231">
+      <c r="H231">
         <f>IF(G231="","",VLOOKUP(G231,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="232" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H232" t="str">
+    <row r="232">
+      <c r="H232">
         <f>IF(G232="","",VLOOKUP(G232,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="233" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H233" t="str">
+    <row r="233">
+      <c r="H233">
         <f>IF(G233="","",VLOOKUP(G233,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="234" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H234" t="str">
+    <row r="234">
+      <c r="H234">
         <f>IF(G234="","",VLOOKUP(G234,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="235" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H235" t="str">
+    <row r="235">
+      <c r="H235">
         <f>IF(G235="","",VLOOKUP(G235,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="236" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H236" t="str">
+    <row r="236">
+      <c r="H236">
         <f>IF(G236="","",VLOOKUP(G236,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="237" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H237" t="str">
+    <row r="237">
+      <c r="H237">
         <f>IF(G237="","",VLOOKUP(G237,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="238" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H238" t="str">
+    <row r="238">
+      <c r="H238">
         <f>IF(G238="","",VLOOKUP(G238,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="239" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H239" t="str">
+    <row r="239">
+      <c r="H239">
         <f>IF(G239="","",VLOOKUP(G239,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="240" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H240" t="str">
+    <row r="240">
+      <c r="H240">
         <f>IF(G240="","",VLOOKUP(G240,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="241" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H241" t="str">
+    <row r="241">
+      <c r="H241">
         <f>IF(G241="","",VLOOKUP(G241,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="242" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H242" t="str">
+    <row r="242">
+      <c r="H242">
         <f>IF(G242="","",VLOOKUP(G242,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="243" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H243" t="str">
+    <row r="243">
+      <c r="H243">
         <f>IF(G243="","",VLOOKUP(G243,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="244" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H244" t="str">
+    <row r="244">
+      <c r="H244">
         <f>IF(G244="","",VLOOKUP(G244,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="245" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H245" t="str">
+    <row r="245">
+      <c r="H245">
         <f>IF(G245="","",VLOOKUP(G245,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="246" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H246" t="str">
+    <row r="246">
+      <c r="H246">
         <f>IF(G246="","",VLOOKUP(G246,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="247" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H247" t="str">
+    <row r="247">
+      <c r="H247">
         <f>IF(G247="","",VLOOKUP(G247,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="248" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H248" t="str">
+    <row r="248">
+      <c r="H248">
         <f>IF(G248="","",VLOOKUP(G248,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="249" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H249" t="str">
+    <row r="249">
+      <c r="H249">
         <f>IF(G249="","",VLOOKUP(G249,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="250" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H250" t="str">
+    <row r="250">
+      <c r="H250">
         <f>IF(G250="","",VLOOKUP(G250,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="251" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H251" t="str">
+    <row r="251">
+      <c r="H251">
         <f>IF(G251="","",VLOOKUP(G251,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="252" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H252" t="str">
+    <row r="252">
+      <c r="H252">
         <f>IF(G252="","",VLOOKUP(G252,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="253" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H253" t="str">
+    <row r="253">
+      <c r="H253">
         <f>IF(G253="","",VLOOKUP(G253,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="254" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H254" t="str">
+    <row r="254">
+      <c r="H254">
         <f>IF(G254="","",VLOOKUP(G254,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="255" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H255" t="str">
+    <row r="255">
+      <c r="H255">
         <f>IF(G255="","",VLOOKUP(G255,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="256" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H256" t="str">
+    <row r="256">
+      <c r="H256">
         <f>IF(G256="","",VLOOKUP(G256,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="257" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H257" t="str">
+    <row r="257">
+      <c r="H257">
         <f>IF(G257="","",VLOOKUP(G257,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="258" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H258" t="str">
+    <row r="258">
+      <c r="H258">
         <f>IF(G258="","",VLOOKUP(G258,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="259" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H259" t="str">
+    <row r="259">
+      <c r="H259">
         <f>IF(G259="","",VLOOKUP(G259,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="260" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H260" t="str">
+    <row r="260">
+      <c r="H260">
         <f>IF(G260="","",VLOOKUP(G260,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="261" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H261" t="str">
+    <row r="261">
+      <c r="H261">
         <f>IF(G261="","",VLOOKUP(G261,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="262" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H262" t="str">
+    <row r="262">
+      <c r="H262">
         <f>IF(G262="","",VLOOKUP(G262,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="263" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H263" t="str">
+    <row r="263">
+      <c r="H263">
         <f>IF(G263="","",VLOOKUP(G263,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="264" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H264" t="str">
+    <row r="264">
+      <c r="H264">
         <f>IF(G264="","",VLOOKUP(G264,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="265" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H265" t="str">
+    <row r="265">
+      <c r="H265">
         <f>IF(G265="","",VLOOKUP(G265,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="266" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H266" t="str">
+    <row r="266">
+      <c r="H266">
         <f>IF(G266="","",VLOOKUP(G266,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="267" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H267" t="str">
+    <row r="267">
+      <c r="H267">
         <f>IF(G267="","",VLOOKUP(G267,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="268" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H268" t="str">
+    <row r="268">
+      <c r="H268">
         <f>IF(G268="","",VLOOKUP(G268,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="269" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H269" t="str">
+    <row r="269">
+      <c r="H269">
         <f>IF(G269="","",VLOOKUP(G269,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="270" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H270" t="str">
+    <row r="270">
+      <c r="H270">
         <f>IF(G270="","",VLOOKUP(G270,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="271" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H271" t="str">
+    <row r="271">
+      <c r="H271">
         <f>IF(G271="","",VLOOKUP(G271,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="272" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H272" t="str">
+    <row r="272">
+      <c r="H272">
         <f>IF(G272="","",VLOOKUP(G272,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="273" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H273" t="str">
+    <row r="273">
+      <c r="H273">
         <f>IF(G273="","",VLOOKUP(G273,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="274" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H274" t="str">
+    <row r="274">
+      <c r="H274">
         <f>IF(G274="","",VLOOKUP(G274,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="275" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H275" t="str">
+    <row r="275">
+      <c r="H275">
         <f>IF(G275="","",VLOOKUP(G275,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="276" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H276" t="str">
+    <row r="276">
+      <c r="H276">
         <f>IF(G276="","",VLOOKUP(G276,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="277" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H277" t="str">
+    <row r="277">
+      <c r="H277">
         <f>IF(G277="","",VLOOKUP(G277,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="278" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H278" t="str">
+    <row r="278">
+      <c r="H278">
         <f>IF(G278="","",VLOOKUP(G278,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="279" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H279" t="str">
+    <row r="279">
+      <c r="H279">
         <f>IF(G279="","",VLOOKUP(G279,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="280" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H280" t="str">
+    <row r="280">
+      <c r="H280">
         <f>IF(G280="","",VLOOKUP(G280,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="281" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H281" t="str">
+    <row r="281">
+      <c r="H281">
         <f>IF(G281="","",VLOOKUP(G281,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="282" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H282" t="str">
+    <row r="282">
+      <c r="H282">
         <f>IF(G282="","",VLOOKUP(G282,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="283" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H283" t="str">
+    <row r="283">
+      <c r="H283">
         <f>IF(G283="","",VLOOKUP(G283,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="284" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H284" t="str">
+    <row r="284">
+      <c r="H284">
         <f>IF(G284="","",VLOOKUP(G284,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="285" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H285" t="str">
+    <row r="285">
+      <c r="H285">
         <f>IF(G285="","",VLOOKUP(G285,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="286" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H286" t="str">
+    <row r="286">
+      <c r="H286">
         <f>IF(G286="","",VLOOKUP(G286,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="287" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H287" t="str">
+    <row r="287">
+      <c r="H287">
         <f>IF(G287="","",VLOOKUP(G287,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="288" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H288" t="str">
+    <row r="288">
+      <c r="H288">
         <f>IF(G288="","",VLOOKUP(G288,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="289" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H289" t="str">
+    <row r="289">
+      <c r="H289">
         <f>IF(G289="","",VLOOKUP(G289,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="290" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H290" t="str">
+    <row r="290">
+      <c r="H290">
         <f>IF(G290="","",VLOOKUP(G290,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="291" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H291" t="str">
+    <row r="291">
+      <c r="H291">
         <f>IF(G291="","",VLOOKUP(G291,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="292" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H292" t="str">
+    <row r="292">
+      <c r="H292">
         <f>IF(G292="","",VLOOKUP(G292,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="293" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H293" t="str">
+    <row r="293">
+      <c r="H293">
         <f>IF(G293="","",VLOOKUP(G293,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="294" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H294" t="str">
+    <row r="294">
+      <c r="H294">
         <f>IF(G294="","",VLOOKUP(G294,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="295" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H295" t="str">
+    <row r="295">
+      <c r="H295">
         <f>IF(G295="","",VLOOKUP(G295,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="296" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H296" t="str">
+    <row r="296">
+      <c r="H296">
         <f>IF(G296="","",VLOOKUP(G296,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="297" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H297" t="str">
+    <row r="297">
+      <c r="H297">
         <f>IF(G297="","",VLOOKUP(G297,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="298" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H298" t="str">
+    <row r="298">
+      <c r="H298">
         <f>IF(G298="","",VLOOKUP(G298,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="299" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H299" t="str">
+    <row r="299">
+      <c r="H299">
         <f>IF(G299="","",VLOOKUP(G299,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="300" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H300" t="str">
+    <row r="300">
+      <c r="H300">
         <f>IF(G300="","",VLOOKUP(G300,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="301" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H301" t="str">
+    <row r="301">
+      <c r="H301">
         <f>IF(G301="","",VLOOKUP(G301,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="302" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H302" t="str">
+    <row r="302">
+      <c r="H302">
         <f>IF(G302="","",VLOOKUP(G302,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="303" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H303" t="str">
+    <row r="303">
+      <c r="H303">
         <f>IF(G303="","",VLOOKUP(G303,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="304" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H304" t="str">
+    <row r="304">
+      <c r="H304">
         <f>IF(G304="","",VLOOKUP(G304,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="305" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H305" t="str">
+    <row r="305">
+      <c r="H305">
         <f>IF(G305="","",VLOOKUP(G305,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="306" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H306" t="str">
+    <row r="306">
+      <c r="H306">
         <f>IF(G306="","",VLOOKUP(G306,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="307" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H307" t="str">
+    <row r="307">
+      <c r="H307">
         <f>IF(G307="","",VLOOKUP(G307,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="308" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H308" t="str">
+    <row r="308">
+      <c r="H308">
         <f>IF(G308="","",VLOOKUP(G308,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="309" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H309" t="str">
+    <row r="309">
+      <c r="H309">
         <f>IF(G309="","",VLOOKUP(G309,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="310" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H310" t="str">
+    <row r="310">
+      <c r="H310">
         <f>IF(G310="","",VLOOKUP(G310,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="311" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H311" t="str">
+    <row r="311">
+      <c r="H311">
         <f>IF(G311="","",VLOOKUP(G311,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="312" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H312" t="str">
+    <row r="312">
+      <c r="H312">
         <f>IF(G312="","",VLOOKUP(G312,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="313" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H313" t="str">
+    <row r="313">
+      <c r="H313">
         <f>IF(G313="","",VLOOKUP(G313,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="314" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H314" t="str">
+    <row r="314">
+      <c r="H314">
         <f>IF(G314="","",VLOOKUP(G314,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="315" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H315" t="str">
+    <row r="315">
+      <c r="H315">
         <f>IF(G315="","",VLOOKUP(G315,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="316" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H316" t="str">
+    <row r="316">
+      <c r="H316">
         <f>IF(G316="","",VLOOKUP(G316,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="317" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H317" t="str">
+    <row r="317">
+      <c r="H317">
         <f>IF(G317="","",VLOOKUP(G317,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="318" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H318" t="str">
+    <row r="318">
+      <c r="H318">
         <f>IF(G318="","",VLOOKUP(G318,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="319" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H319" t="str">
+    <row r="319">
+      <c r="H319">
         <f>IF(G319="","",VLOOKUP(G319,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="320" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H320" t="str">
+    <row r="320">
+      <c r="H320">
         <f>IF(G320="","",VLOOKUP(G320,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="321" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H321" t="str">
+    <row r="321">
+      <c r="H321">
         <f>IF(G321="","",VLOOKUP(G321,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="322" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H322" t="str">
+    <row r="322">
+      <c r="H322">
         <f>IF(G322="","",VLOOKUP(G322,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="323" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H323" t="str">
+    <row r="323">
+      <c r="H323">
         <f>IF(G323="","",VLOOKUP(G323,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="324" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H324" t="str">
+    <row r="324">
+      <c r="H324">
         <f>IF(G324="","",VLOOKUP(G324,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="325" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H325" t="str">
+    <row r="325">
+      <c r="H325">
         <f>IF(G325="","",VLOOKUP(G325,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="326" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H326" t="str">
+    <row r="326">
+      <c r="H326">
         <f>IF(G326="","",VLOOKUP(G326,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="327" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H327" t="str">
+    <row r="327">
+      <c r="H327">
         <f>IF(G327="","",VLOOKUP(G327,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="328" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H328" t="str">
+    <row r="328">
+      <c r="H328">
         <f>IF(G328="","",VLOOKUP(G328,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="329" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H329" t="str">
+    <row r="329">
+      <c r="H329">
         <f>IF(G329="","",VLOOKUP(G329,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="330" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H330" t="str">
+    <row r="330">
+      <c r="H330">
         <f>IF(G330="","",VLOOKUP(G330,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="331" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H331" t="str">
+    <row r="331">
+      <c r="H331">
         <f>IF(G331="","",VLOOKUP(G331,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="332" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H332" t="str">
+    <row r="332">
+      <c r="H332">
         <f>IF(G332="","",VLOOKUP(G332,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="333" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H333" t="str">
+    <row r="333">
+      <c r="H333">
         <f>IF(G333="","",VLOOKUP(G333,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="334" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H334" t="str">
+    <row r="334">
+      <c r="H334">
         <f>IF(G334="","",VLOOKUP(G334,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="335" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H335" t="str">
+    <row r="335">
+      <c r="H335">
         <f>IF(G335="","",VLOOKUP(G335,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="336" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H336" t="str">
+    <row r="336">
+      <c r="H336">
         <f>IF(G336="","",VLOOKUP(G336,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="337" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H337" t="str">
+    <row r="337">
+      <c r="H337">
         <f>IF(G337="","",VLOOKUP(G337,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="338" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H338" t="str">
+    <row r="338">
+      <c r="H338">
         <f>IF(G338="","",VLOOKUP(G338,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="339" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H339" t="str">
+    <row r="339">
+      <c r="H339">
         <f>IF(G339="","",VLOOKUP(G339,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="340" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H340" t="str">
+    <row r="340">
+      <c r="H340">
         <f>IF(G340="","",VLOOKUP(G340,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="341" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H341" t="str">
+    <row r="341">
+      <c r="H341">
         <f>IF(G341="","",VLOOKUP(G341,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="342" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H342" t="str">
+    <row r="342">
+      <c r="H342">
         <f>IF(G342="","",VLOOKUP(G342,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="343" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H343" t="str">
+    <row r="343">
+      <c r="H343">
         <f>IF(G343="","",VLOOKUP(G343,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="344" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H344" t="str">
+    <row r="344">
+      <c r="H344">
         <f>IF(G344="","",VLOOKUP(G344,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="345" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H345" t="str">
+    <row r="345">
+      <c r="H345">
         <f>IF(G345="","",VLOOKUP(G345,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="346" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H346" t="str">
+    <row r="346">
+      <c r="H346">
         <f>IF(G346="","",VLOOKUP(G346,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="347" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H347" t="str">
+    <row r="347">
+      <c r="H347">
         <f>IF(G347="","",VLOOKUP(G347,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="348" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H348" t="str">
+    <row r="348">
+      <c r="H348">
         <f>IF(G348="","",VLOOKUP(G348,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="349" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H349" t="str">
+    <row r="349">
+      <c r="H349">
         <f>IF(G349="","",VLOOKUP(G349,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="350" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H350" t="str">
+    <row r="350">
+      <c r="H350">
         <f>IF(G350="","",VLOOKUP(G350,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="351" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H351" t="str">
+    <row r="351">
+      <c r="H351">
         <f>IF(G351="","",VLOOKUP(G351,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="352" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H352" t="str">
+    <row r="352">
+      <c r="H352">
         <f>IF(G352="","",VLOOKUP(G352,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="353" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H353" t="str">
+    <row r="353">
+      <c r="H353">
         <f>IF(G353="","",VLOOKUP(G353,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="354" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H354" t="str">
+    <row r="354">
+      <c r="H354">
         <f>IF(G354="","",VLOOKUP(G354,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="355" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H355" t="str">
+    <row r="355">
+      <c r="H355">
         <f>IF(G355="","",VLOOKUP(G355,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="356" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H356" t="str">
+    <row r="356">
+      <c r="H356">
         <f>IF(G356="","",VLOOKUP(G356,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="357" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H357" t="str">
+    <row r="357">
+      <c r="H357">
         <f>IF(G357="","",VLOOKUP(G357,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="358" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H358" t="str">
+    <row r="358">
+      <c r="H358">
         <f>IF(G358="","",VLOOKUP(G358,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="359" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H359" t="str">
+    <row r="359">
+      <c r="H359">
         <f>IF(G359="","",VLOOKUP(G359,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="360" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H360" t="str">
+    <row r="360">
+      <c r="H360">
         <f>IF(G360="","",VLOOKUP(G360,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="361" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H361" t="str">
+    <row r="361">
+      <c r="H361">
         <f>IF(G361="","",VLOOKUP(G361,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="362" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H362" t="str">
+    <row r="362">
+      <c r="H362">
         <f>IF(G362="","",VLOOKUP(G362,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="363" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H363" t="str">
+    <row r="363">
+      <c r="H363">
         <f>IF(G363="","",VLOOKUP(G363,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="364" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H364" t="str">
+    <row r="364">
+      <c r="H364">
         <f>IF(G364="","",VLOOKUP(G364,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="365" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H365" t="str">
+    <row r="365">
+      <c r="H365">
         <f>IF(G365="","",VLOOKUP(G365,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="366" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H366" t="str">
+    <row r="366">
+      <c r="H366">
         <f>IF(G366="","",VLOOKUP(G366,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="367" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H367" t="str">
+    <row r="367">
+      <c r="H367">
         <f>IF(G367="","",VLOOKUP(G367,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="368" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H368" t="str">
+    <row r="368">
+      <c r="H368">
         <f>IF(G368="","",VLOOKUP(G368,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="369" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H369" t="str">
+    <row r="369">
+      <c r="H369">
         <f>IF(G369="","",VLOOKUP(G369,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="370" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H370" t="str">
+    <row r="370">
+      <c r="H370">
         <f>IF(G370="","",VLOOKUP(G370,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="371" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H371" t="str">
+    <row r="371">
+      <c r="H371">
         <f>IF(G371="","",VLOOKUP(G371,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="372" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H372" t="str">
+    <row r="372">
+      <c r="H372">
         <f>IF(G372="","",VLOOKUP(G372,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="373" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H373" t="str">
+    <row r="373">
+      <c r="H373">
         <f>IF(G373="","",VLOOKUP(G373,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="374" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H374" t="str">
+    <row r="374">
+      <c r="H374">
         <f>IF(G374="","",VLOOKUP(G374,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="375" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H375" t="str">
+    <row r="375">
+      <c r="H375">
         <f>IF(G375="","",VLOOKUP(G375,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="376" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H376" t="str">
+    <row r="376">
+      <c r="H376">
         <f>IF(G376="","",VLOOKUP(G376,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="377" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H377" t="str">
+    <row r="377">
+      <c r="H377">
         <f>IF(G377="","",VLOOKUP(G377,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="378" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H378" t="str">
+    <row r="378">
+      <c r="H378">
         <f>IF(G378="","",VLOOKUP(G378,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="379" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H379" t="str">
+    <row r="379">
+      <c r="H379">
         <f>IF(G379="","",VLOOKUP(G379,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="380" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H380" t="str">
+    <row r="380">
+      <c r="H380">
         <f>IF(G380="","",VLOOKUP(G380,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="381" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H381" t="str">
+    <row r="381">
+      <c r="H381">
         <f>IF(G381="","",VLOOKUP(G381,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="382" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H382" t="str">
+    <row r="382">
+      <c r="H382">
         <f>IF(G382="","",VLOOKUP(G382,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="383" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H383" t="str">
+    <row r="383">
+      <c r="H383">
         <f>IF(G383="","",VLOOKUP(G383,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="384" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H384" t="str">
+    <row r="384">
+      <c r="H384">
         <f>IF(G384="","",VLOOKUP(G384,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="385" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H385" t="str">
+    <row r="385">
+      <c r="H385">
         <f>IF(G385="","",VLOOKUP(G385,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="386" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H386" t="str">
+    <row r="386">
+      <c r="H386">
         <f>IF(G386="","",VLOOKUP(G386,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="387" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H387" t="str">
+    <row r="387">
+      <c r="H387">
         <f>IF(G387="","",VLOOKUP(G387,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="388" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H388" t="str">
+    <row r="388">
+      <c r="H388">
         <f>IF(G388="","",VLOOKUP(G388,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="389" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H389" t="str">
+    <row r="389">
+      <c r="H389">
         <f>IF(G389="","",VLOOKUP(G389,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="390" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H390" t="str">
+    <row r="390">
+      <c r="H390">
         <f>IF(G390="","",VLOOKUP(G390,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="391" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H391" t="str">
+    <row r="391">
+      <c r="H391">
         <f>IF(G391="","",VLOOKUP(G391,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="392" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H392" t="str">
+    <row r="392">
+      <c r="H392">
         <f>IF(G392="","",VLOOKUP(G392,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="393" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H393" t="str">
+    <row r="393">
+      <c r="H393">
         <f>IF(G393="","",VLOOKUP(G393,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="394" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H394" t="str">
+    <row r="394">
+      <c r="H394">
         <f>IF(G394="","",VLOOKUP(G394,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="395" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H395" t="str">
+    <row r="395">
+      <c r="H395">
         <f>IF(G395="","",VLOOKUP(G395,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="396" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H396" t="str">
+    <row r="396">
+      <c r="H396">
         <f>IF(G396="","",VLOOKUP(G396,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="397" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H397" t="str">
+    <row r="397">
+      <c r="H397">
         <f>IF(G397="","",VLOOKUP(G397,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="398" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H398" t="str">
+    <row r="398">
+      <c r="H398">
         <f>IF(G398="","",VLOOKUP(G398,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="399" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H399" t="str">
+    <row r="399">
+      <c r="H399">
         <f>IF(G399="","",VLOOKUP(G399,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="400" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H400" t="str">
+    <row r="400">
+      <c r="H400">
         <f>IF(G400="","",VLOOKUP(G400,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="401" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H401" t="str">
+    <row r="401">
+      <c r="H401">
         <f>IF(G401="","",VLOOKUP(G401,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="402" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H402" t="str">
+    <row r="402">
+      <c r="H402">
         <f>IF(G402="","",VLOOKUP(G402,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="403" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H403" t="str">
+    <row r="403">
+      <c r="H403">
         <f>IF(G403="","",VLOOKUP(G403,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="404" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H404" t="str">
+    <row r="404">
+      <c r="H404">
         <f>IF(G404="","",VLOOKUP(G404,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="405" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H405" t="str">
+    <row r="405">
+      <c r="H405">
         <f>IF(G405="","",VLOOKUP(G405,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="406" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H406" t="str">
+    <row r="406">
+      <c r="H406">
         <f>IF(G406="","",VLOOKUP(G406,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="407" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H407" t="str">
+    <row r="407">
+      <c r="H407">
         <f>IF(G407="","",VLOOKUP(G407,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="408" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H408" t="str">
+    <row r="408">
+      <c r="H408">
         <f>IF(G408="","",VLOOKUP(G408,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="409" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H409" t="str">
+    <row r="409">
+      <c r="H409">
         <f>IF(G409="","",VLOOKUP(G409,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="410" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H410" t="str">
+    <row r="410">
+      <c r="H410">
         <f>IF(G410="","",VLOOKUP(G410,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="411" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H411" t="str">
+    <row r="411">
+      <c r="H411">
         <f>IF(G411="","",VLOOKUP(G411,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="412" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H412" t="str">
+    <row r="412">
+      <c r="H412">
         <f>IF(G412="","",VLOOKUP(G412,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="413" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H413" t="str">
+    <row r="413">
+      <c r="H413">
         <f>IF(G413="","",VLOOKUP(G413,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="414" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H414" t="str">
+    <row r="414">
+      <c r="H414">
         <f>IF(G414="","",VLOOKUP(G414,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="415" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H415" t="str">
+    <row r="415">
+      <c r="H415">
         <f>IF(G415="","",VLOOKUP(G415,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="416" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H416" t="str">
+    <row r="416">
+      <c r="H416">
         <f>IF(G416="","",VLOOKUP(G416,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="417" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H417" t="str">
+    <row r="417">
+      <c r="H417">
         <f>IF(G417="","",VLOOKUP(G417,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="418" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H418" t="str">
+    <row r="418">
+      <c r="H418">
         <f>IF(G418="","",VLOOKUP(G418,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="419" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H419" t="str">
+    <row r="419">
+      <c r="H419">
         <f>IF(G419="","",VLOOKUP(G419,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="420" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H420" t="str">
+    <row r="420">
+      <c r="H420">
         <f>IF(G420="","",VLOOKUP(G420,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="421" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H421" t="str">
+    <row r="421">
+      <c r="H421">
         <f>IF(G421="","",VLOOKUP(G421,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="422" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H422" t="str">
+    <row r="422">
+      <c r="H422">
         <f>IF(G422="","",VLOOKUP(G422,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="423" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H423" t="str">
+    <row r="423">
+      <c r="H423">
         <f>IF(G423="","",VLOOKUP(G423,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="424" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H424" t="str">
+    <row r="424">
+      <c r="H424">
         <f>IF(G424="","",VLOOKUP(G424,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="425" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H425" t="str">
+    <row r="425">
+      <c r="H425">
         <f>IF(G425="","",VLOOKUP(G425,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="426" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H426" t="str">
+    <row r="426">
+      <c r="H426">
         <f>IF(G426="","",VLOOKUP(G426,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="427" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H427" t="str">
+    <row r="427">
+      <c r="H427">
         <f>IF(G427="","",VLOOKUP(G427,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="428" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H428" t="str">
+    <row r="428">
+      <c r="H428">
         <f>IF(G428="","",VLOOKUP(G428,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="429" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H429" t="str">
+    <row r="429">
+      <c r="H429">
         <f>IF(G429="","",VLOOKUP(G429,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="430" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H430" t="str">
+    <row r="430">
+      <c r="H430">
         <f>IF(G430="","",VLOOKUP(G430,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="431" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H431" t="str">
+    <row r="431">
+      <c r="H431">
         <f>IF(G431="","",VLOOKUP(G431,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="432" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H432" t="str">
+    <row r="432">
+      <c r="H432">
         <f>IF(G432="","",VLOOKUP(G432,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="433" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H433" t="str">
+    <row r="433">
+      <c r="H433">
         <f>IF(G433="","",VLOOKUP(G433,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="434" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H434" t="str">
+    <row r="434">
+      <c r="H434">
         <f>IF(G434="","",VLOOKUP(G434,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="435" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H435" t="str">
+    <row r="435">
+      <c r="H435">
         <f>IF(G435="","",VLOOKUP(G435,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="436" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H436" t="str">
+    <row r="436">
+      <c r="H436">
         <f>IF(G436="","",VLOOKUP(G436,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="437" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H437" t="str">
+    <row r="437">
+      <c r="H437">
         <f>IF(G437="","",VLOOKUP(G437,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="438" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H438" t="str">
+    <row r="438">
+      <c r="H438">
         <f>IF(G438="","",VLOOKUP(G438,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="439" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H439" t="str">
+    <row r="439">
+      <c r="H439">
         <f>IF(G439="","",VLOOKUP(G439,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="440" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H440" t="str">
+    <row r="440">
+      <c r="H440">
         <f>IF(G440="","",VLOOKUP(G440,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="441" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H441" t="str">
+    <row r="441">
+      <c r="H441">
         <f>IF(G441="","",VLOOKUP(G441,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="442" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H442" t="str">
+    <row r="442">
+      <c r="H442">
         <f>IF(G442="","",VLOOKUP(G442,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="443" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H443" t="str">
+    <row r="443">
+      <c r="H443">
         <f>IF(G443="","",VLOOKUP(G443,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="444" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H444" t="str">
+    <row r="444">
+      <c r="H444">
         <f>IF(G444="","",VLOOKUP(G444,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="445" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H445" t="str">
+    <row r="445">
+      <c r="H445">
         <f>IF(G445="","",VLOOKUP(G445,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="446" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H446" t="str">
+    <row r="446">
+      <c r="H446">
         <f>IF(G446="","",VLOOKUP(G446,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="447" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H447" t="str">
+    <row r="447">
+      <c r="H447">
         <f>IF(G447="","",VLOOKUP(G447,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="448" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H448" t="str">
+    <row r="448">
+      <c r="H448">
         <f>IF(G448="","",VLOOKUP(G448,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="449" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H449" t="str">
+    <row r="449">
+      <c r="H449">
         <f>IF(G449="","",VLOOKUP(G449,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="450" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H450" t="str">
+    <row r="450">
+      <c r="H450">
         <f>IF(G450="","",VLOOKUP(G450,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="451" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H451" t="str">
+    <row r="451">
+      <c r="H451">
         <f>IF(G451="","",VLOOKUP(G451,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="452" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H452" t="str">
+    <row r="452">
+      <c r="H452">
         <f>IF(G452="","",VLOOKUP(G452,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="453" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H453" t="str">
+    <row r="453">
+      <c r="H453">
         <f>IF(G453="","",VLOOKUP(G453,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="454" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H454" t="str">
+    <row r="454">
+      <c r="H454">
         <f>IF(G454="","",VLOOKUP(G454,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="455" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H455" t="str">
+    <row r="455">
+      <c r="H455">
         <f>IF(G455="","",VLOOKUP(G455,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="456" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H456" t="str">
+    <row r="456">
+      <c r="H456">
         <f>IF(G456="","",VLOOKUP(G456,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="457" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H457" t="str">
+    <row r="457">
+      <c r="H457">
         <f>IF(G457="","",VLOOKUP(G457,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="458" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H458" t="str">
+    <row r="458">
+      <c r="H458">
         <f>IF(G458="","",VLOOKUP(G458,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="459" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H459" t="str">
+    <row r="459">
+      <c r="H459">
         <f>IF(G459="","",VLOOKUP(G459,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="460" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H460" t="str">
+    <row r="460">
+      <c r="H460">
         <f>IF(G460="","",VLOOKUP(G460,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="461" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H461" t="str">
+    <row r="461">
+      <c r="H461">
         <f>IF(G461="","",VLOOKUP(G461,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="462" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H462" t="str">
+    <row r="462">
+      <c r="H462">
         <f>IF(G462="","",VLOOKUP(G462,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="463" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H463" t="str">
+    <row r="463">
+      <c r="H463">
         <f>IF(G463="","",VLOOKUP(G463,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="464" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H464" t="str">
+    <row r="464">
+      <c r="H464">
         <f>IF(G464="","",VLOOKUP(G464,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="465" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H465" t="str">
+    <row r="465">
+      <c r="H465">
         <f>IF(G465="","",VLOOKUP(G465,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="466" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H466" t="str">
+    <row r="466">
+      <c r="H466">
         <f>IF(G466="","",VLOOKUP(G466,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="467" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H467" t="str">
+    <row r="467">
+      <c r="H467">
         <f>IF(G467="","",VLOOKUP(G467,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="468" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H468" t="str">
+    <row r="468">
+      <c r="H468">
         <f>IF(G468="","",VLOOKUP(G468,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="469" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H469" t="str">
+    <row r="469">
+      <c r="H469">
         <f>IF(G469="","",VLOOKUP(G469,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="470" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H470" t="str">
+    <row r="470">
+      <c r="H470">
         <f>IF(G470="","",VLOOKUP(G470,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="471" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H471" t="str">
+    <row r="471">
+      <c r="H471">
         <f>IF(G471="","",VLOOKUP(G471,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="472" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H472" t="str">
+    <row r="472">
+      <c r="H472">
         <f>IF(G472="","",VLOOKUP(G472,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="473" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H473" t="str">
+    <row r="473">
+      <c r="H473">
         <f>IF(G473="","",VLOOKUP(G473,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="474" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H474" t="str">
+    <row r="474">
+      <c r="H474">
         <f>IF(G474="","",VLOOKUP(G474,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="475" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H475" t="str">
+    <row r="475">
+      <c r="H475">
         <f>IF(G475="","",VLOOKUP(G475,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="476" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H476" t="str">
+    <row r="476">
+      <c r="H476">
         <f>IF(G476="","",VLOOKUP(G476,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="477" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H477" t="str">
+    <row r="477">
+      <c r="H477">
         <f>IF(G477="","",VLOOKUP(G477,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="478" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H478" t="str">
+    <row r="478">
+      <c r="H478">
         <f>IF(G478="","",VLOOKUP(G478,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="479" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H479" t="str">
+    <row r="479">
+      <c r="H479">
         <f>IF(G479="","",VLOOKUP(G479,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="480" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H480" t="str">
+    <row r="480">
+      <c r="H480">
         <f>IF(G480="","",VLOOKUP(G480,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="481" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H481" t="str">
+    <row r="481">
+      <c r="H481">
         <f>IF(G481="","",VLOOKUP(G481,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="482" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H482" t="str">
+    <row r="482">
+      <c r="H482">
         <f>IF(G482="","",VLOOKUP(G482,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="483" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H483" t="str">
+    <row r="483">
+      <c r="H483">
         <f>IF(G483="","",VLOOKUP(G483,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="484" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H484" t="str">
+    <row r="484">
+      <c r="H484">
         <f>IF(G484="","",VLOOKUP(G484,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="485" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H485" t="str">
+    <row r="485">
+      <c r="H485">
         <f>IF(G485="","",VLOOKUP(G485,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="486" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H486" t="str">
+    <row r="486">
+      <c r="H486">
         <f>IF(G486="","",VLOOKUP(G486,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="487" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H487" t="str">
+    <row r="487">
+      <c r="H487">
         <f>IF(G487="","",VLOOKUP(G487,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="488" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H488" t="str">
+    <row r="488">
+      <c r="H488">
         <f>IF(G488="","",VLOOKUP(G488,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="489" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H489" t="str">
+    <row r="489">
+      <c r="H489">
         <f>IF(G489="","",VLOOKUP(G489,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="490" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H490" t="str">
+    <row r="490">
+      <c r="H490">
         <f>IF(G490="","",VLOOKUP(G490,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="491" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H491" t="str">
+    <row r="491">
+      <c r="H491">
         <f>IF(G491="","",VLOOKUP(G491,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="492" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H492" t="str">
+    <row r="492">
+      <c r="H492">
         <f>IF(G492="","",VLOOKUP(G492,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="493" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H493" t="str">
+    <row r="493">
+      <c r="H493">
         <f>IF(G493="","",VLOOKUP(G493,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="494" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H494" t="str">
+    <row r="494">
+      <c r="H494">
         <f>IF(G494="","",VLOOKUP(G494,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="495" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H495" t="str">
+    <row r="495">
+      <c r="H495">
         <f>IF(G495="","",VLOOKUP(G495,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="496" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H496" t="str">
+    <row r="496">
+      <c r="H496">
         <f>IF(G496="","",VLOOKUP(G496,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="497" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H497" t="str">
+    <row r="497">
+      <c r="H497">
         <f>IF(G497="","",VLOOKUP(G497,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="498" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H498" t="str">
+    <row r="498">
+      <c r="H498">
         <f>IF(G498="","",VLOOKUP(G498,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="499" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H499" t="str">
+    <row r="499">
+      <c r="H499">
         <f>IF(G499="","",VLOOKUP(G499,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
-    <row r="500" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H500" t="str">
+    <row r="500">
+      <c r="H500">
         <f>IF(G500="","",VLOOKUP(G500,REFERENCIA!$A$1:$B$15,2,0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>REFERENCIA!$A$1:$A$15</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G500</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN FUERA DE VISUAL / CON OBSTRUCCIÓN.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN CON USUARIO NO CORRESPONDIENTE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NO SE COMPLETA EL PROCESO DE FISCALIZACION Y SE ELIMINA.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
       </c>
     </row>
   </sheetData>
